--- a/tests/fixtures/byte-gate/sheet-row-breaks.xlsx
+++ b/tests/fixtures/byte-gate/sheet-row-breaks.xlsx
@@ -1405,6 +1405,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageSetup paperSize="9" orientation="landscape"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="20" max="16383" man="1"/>
